--- a/GEMAS_DEFINITIVO.xlsx
+++ b/GEMAS_DEFINITIVO.xlsx
@@ -650,7 +650,7 @@
     <xf numFmtId="3" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -673,64 +673,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="23">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Century Gothic"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF2E4057"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Century Gothic"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF0F4F8"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1496,22 +1438,80 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
         <bottom style="thin">
           <color rgb="FFCCCCCC"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Century Gothic"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF0F4F8"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Century Gothic"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF2E4057"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FFCCCCCC"/>
         </left>
-        <top style="thin">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -1528,31 +1528,31 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DBC61563-8C81-40BB-B1FB-E195B39FE187}" name="Tabla1" displayName="Tabla1" ref="A1:U14" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="21" tableBorderDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DBC61563-8C81-40BB-B1FB-E195B39FE187}" name="Tabla1" displayName="Tabla1" ref="A1:U14" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19">
   <autoFilter ref="A1:U14" xr:uid="{DBC61563-8C81-40BB-B1FB-E195B39FE187}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{16740106-C1FE-4A93-B016-8D68E510D83F}" name="SKU" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{09A192B8-EAAF-4898-B7A3-F90504B18A79}" name="Gema" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{BA1F56EB-D3BE-4716-9DEF-47D31BC9DD3E}" name="Peso (ct)" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{E39BC5CE-832F-44BE-A092-CEFC64B086AB}" name="Dimensiones (mm)" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{7734DC0C-F613-46CA-A9FD-D261BFBAF1B7}" name="Certificado" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{6ED00A05-643C-414D-9C50-3D8AAFBE7960}" name="Color" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{127D106F-9E1F-4BD6-B9DD-8C3E3AFDFFB9}" name="Tratamiento" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{C398D847-DE8F-4738-95D7-8E61F35A17CA}" name="Sellado" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{A3BEE832-9FB0-4317-8A1A-A5FCB3F946EA}" name="Forma" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{9BEB215A-8BFC-471C-8E6A-FA8981A7D210}" name="Pureza" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{2A3B33DB-A068-4A02-8E78-A27DAB77D921}" name="Origen" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{EFD16298-68B4-4A15-AD98-04ED7C2D4E89}" name="Notas" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{16740106-C1FE-4A93-B016-8D68E510D83F}" name="SKU" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{09A192B8-EAAF-4898-B7A3-F90504B18A79}" name="Gema" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{BA1F56EB-D3BE-4716-9DEF-47D31BC9DD3E}" name="Peso (ct)" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{E39BC5CE-832F-44BE-A092-CEFC64B086AB}" name="Dimensiones (mm)" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{7734DC0C-F613-46CA-A9FD-D261BFBAF1B7}" name="Certificado" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{6ED00A05-643C-414D-9C50-3D8AAFBE7960}" name="Color" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{127D106F-9E1F-4BD6-B9DD-8C3E3AFDFFB9}" name="Tratamiento" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{C398D847-DE8F-4738-95D7-8E61F35A17CA}" name="Sellado" dataDxfId="11"/>
+    <tableColumn id="9" xr3:uid="{A3BEE832-9FB0-4317-8A1A-A5FCB3F946EA}" name="Forma" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{9BEB215A-8BFC-471C-8E6A-FA8981A7D210}" name="Pureza" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{2A3B33DB-A068-4A02-8E78-A27DAB77D921}" name="Origen" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{EFD16298-68B4-4A15-AD98-04ED7C2D4E89}" name="Notas" dataDxfId="7"/>
     <tableColumn id="13" xr3:uid="{8C6CBABC-AEE1-40B4-98BD-0BD9BBF2C7BD}" name="Fecha de compra"/>
-    <tableColumn id="14" xr3:uid="{6371D893-C2F0-4442-93DB-9230BCDDA4C1}" name="Vendedor" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{1717A4CA-E348-4F86-B897-57D4D3CDF3F6}" name="Precio" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{C4EE19D8-88C6-41C7-9AE5-A93E96F58D68}" name="Portes" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{6DA5F09A-D9D0-4E7C-810E-FF17F36D3928}" name="Total" dataDxfId="5">
+    <tableColumn id="14" xr3:uid="{6371D893-C2F0-4442-93DB-9230BCDDA4C1}" name="Vendedor" dataDxfId="6"/>
+    <tableColumn id="15" xr3:uid="{1717A4CA-E348-4F86-B897-57D4D3CDF3F6}" name="Precio" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{C4EE19D8-88C6-41C7-9AE5-A93E96F58D68}" name="Portes" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{6DA5F09A-D9D0-4E7C-810E-FF17F36D3928}" name="Total" dataDxfId="3">
       <calculatedColumnFormula>SUM(O2:P2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{144C130E-8431-48D5-862B-666CFE041738}" name="Rango mín." dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{B7BC2C68-0B35-4C8D-9733-B57C69D4789A}" name="Rango máx." dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{1FA8A140-6776-4681-A6D8-0A13D4EDCDF4}" name="Ubicación" dataDxfId="2"/>
+    <tableColumn id="18" xr3:uid="{144C130E-8431-48D5-862B-666CFE041738}" name="Rango mín." dataDxfId="2"/>
+    <tableColumn id="19" xr3:uid="{B7BC2C68-0B35-4C8D-9733-B57C69D4789A}" name="Rango máx." dataDxfId="1"/>
+    <tableColumn id="20" xr3:uid="{1FA8A140-6776-4681-A6D8-0A13D4EDCDF4}" name="Ubicación" dataDxfId="0"/>
     <tableColumn id="21" xr3:uid="{4F690BC3-8B45-4F23-A387-5522490E6EB0}" name="Anotaciones"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
